--- a/output/타임테이블_테스트.xlsx
+++ b/output/타임테이블_테스트.xlsx
@@ -1,18 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{313A8F71-823C-4E89-9C8F-A81DE4D5806C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="상담테이블" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="작성 안내" state="visible" r:id="rId5"/>
+    <sheet name="상담테이블" sheetId="1" r:id="rId1"/>
+    <sheet name="작성 안내" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="88">
   <si>
     <t>번호</t>
   </si>
@@ -26,9 +43,6 @@
     <t>부스</t>
   </si>
   <si>
-    <t>05-28</t>
-  </si>
-  <si>
     <t>10:00 - 11:00</t>
   </si>
   <si>
@@ -47,7 +61,7 @@
     <t>15:00 - 16:00</t>
   </si>
   <si>
-    <t xml:space="preserve">(주)구매기업
+    <t>(주)구매기업
 홍구매
 buyer01@excon-test.kr</t>
   </si>
@@ -58,7 +72,7 @@
     <t>A01</t>
   </si>
   <si>
-    <t xml:space="preserve">수출주식회사
+    <t>수출주식회사
 수출주식회사
 김수출 (김수출)
 010-1000-2000
@@ -66,7 +80,7 @@
 seller01@excon-test.kr</t>
   </si>
   <si>
-    <t xml:space="preserve">글로벌수출
+    <t>글로벌수출
 글로벌수출
 이대박 (이대박)
 010-1111-2111
@@ -74,7 +88,7 @@
 seller02@excon-test.kr</t>
   </si>
   <si>
-    <t xml:space="preserve">한국무역
+    <t>한국무역
 한국무역
 박무역 (박무역)
 010-1222-2222
@@ -82,7 +96,7 @@
 seller03@excon-test.kr</t>
   </si>
   <si>
-    <t xml:space="preserve">세계상사
+    <t>세계상사
 세계상사
 최세계 (최세계)
 010-1333-2333
@@ -90,7 +104,7 @@
 seller04@excon-test.kr</t>
   </si>
   <si>
-    <t xml:space="preserve">대박상품
+    <t>대박상품
 대박상품
 정상품 (정상품)
 010-1444-2444
@@ -98,7 +112,7 @@
 seller05@excon-test.kr</t>
   </si>
   <si>
-    <t xml:space="preserve">해외판로
+    <t>해외판로
 해외판로
 강해외 (강해외)
 010-1555-2555
@@ -106,7 +120,7 @@
 seller06@excon-test.kr</t>
   </si>
   <si>
-    <t xml:space="preserve">서신영상사
+    <t>서신영상사
 서신영
 buyer02@excon-test.kr</t>
   </si>
@@ -117,7 +131,7 @@
     <t>A02</t>
   </si>
   <si>
-    <t xml:space="preserve">국제상사
+    <t>국제상사
 국제상사
 조국제 (조국제)
 010-1666-2666
@@ -125,7 +139,7 @@
 seller07@excon-test.kr</t>
   </si>
   <si>
-    <t xml:space="preserve">문상선바이어
+    <t>문상선바이어
 문상선
 buyer03@excon-test.kr</t>
   </si>
@@ -136,7 +150,7 @@
     <t>A03</t>
   </si>
   <si>
-    <t xml:space="preserve">글로벌선
+    <t>글로벌선
 글로벌선
 윤글로벌 (윤글로벌)
 010-1777-2777
@@ -144,7 +158,7 @@
 seller08@excon-test.kr</t>
   </si>
   <si>
-    <t xml:space="preserve">한도매무역
+    <t>한도매무역
 한도매
 buyer04@excon-test.kr</t>
   </si>
@@ -155,7 +169,7 @@
     <t>A04</t>
   </si>
   <si>
-    <t xml:space="preserve">수주코리아
+    <t>수주코리아
 수주코리아
 장수주 (장수주)
 010-1888-2888
@@ -163,7 +177,7 @@
 seller09@excon-test.kr</t>
   </si>
   <si>
-    <t xml:space="preserve">오해외구매
+    <t>오해외구매
 오해외
 buyer05@excon-test.kr</t>
   </si>
@@ -174,7 +188,7 @@
     <t>A05</t>
   </si>
   <si>
-    <t xml:space="preserve">선적무역
+    <t>선적무역
 선적무역
 임선적 (임선적)
 010-1999-2999
@@ -182,7 +196,7 @@
 seller10@excon-test.kr</t>
   </si>
   <si>
-    <t xml:space="preserve">권바이어상사
+    <t>권바이어상사
 권바이어
 buyer06@excon-test.kr</t>
   </si>
@@ -193,7 +207,7 @@
     <t>A06</t>
   </si>
   <si>
-    <t xml:space="preserve">신무역(주)
+    <t>신무역(주)
 신무역
 buyer07@excon-test.kr</t>
   </si>
@@ -204,7 +218,7 @@
     <t>A07</t>
   </si>
   <si>
-    <t xml:space="preserve">백선구글로벌
+    <t>백선구글로벌
 백선구
 buyer08@excon-test.kr</t>
   </si>
@@ -215,7 +229,7 @@
     <t>A08</t>
   </si>
   <si>
-    <t xml:space="preserve">류재고상사
+    <t>류재고상사
 류재고
 buyer09@excon-test.kr</t>
   </si>
@@ -226,7 +240,7 @@
     <t>A09</t>
   </si>
   <si>
-    <t xml:space="preserve">남공급바이어
+    <t>남공급바이어
 남공급
 buyer10@excon-test.kr</t>
   </si>
@@ -237,7 +251,7 @@
     <t>A10</t>
   </si>
   <si>
-    <t xml:space="preserve">심구매기업
+    <t>심구매기업
 심구매2
 buyer11@excon-test.kr</t>
   </si>
@@ -251,7 +265,7 @@
     <t/>
   </si>
   <si>
-    <t xml:space="preserve">노상호상사
+    <t>노상호상사
 노상호
 buyer12@excon-test.kr</t>
   </si>
@@ -262,7 +276,7 @@
     <t>B02</t>
   </si>
   <si>
-    <t xml:space="preserve">구신뢰무역
+    <t>구신뢰무역
 구신뢰
 buyer13@excon-test.kr</t>
   </si>
@@ -273,7 +287,7 @@
     <t>B03</t>
   </si>
   <si>
-    <t xml:space="preserve">안협력바이어
+    <t>안협력바이어
 안협력
 buyer14@excon-test.kr</t>
   </si>
@@ -284,7 +298,7 @@
     <t>B04</t>
   </si>
   <si>
-    <t xml:space="preserve">천계약기업
+    <t>천계약기업
 천계약
 buyer15@excon-test.kr</t>
   </si>
@@ -295,7 +309,7 @@
     <t>B05</t>
   </si>
   <si>
-    <t xml:space="preserve">양상담상사
+    <t>양상담상사
 양상담
 buyer16@excon-test.kr</t>
   </si>
@@ -306,7 +320,7 @@
     <t>B06</t>
   </si>
   <si>
-    <t xml:space="preserve">하수입무역
+    <t>하수입무역
 하수입
 buyer17@excon-test.kr</t>
   </si>
@@ -317,7 +331,7 @@
     <t>B07</t>
   </si>
   <si>
-    <t xml:space="preserve">주상품기업
+    <t>주상품기업
 주상품
 buyer18@excon-test.kr</t>
   </si>
@@ -328,7 +342,7 @@
     <t>B08</t>
   </si>
   <si>
-    <t xml:space="preserve">진해외바이어
+    <t>진해외바이어
 진해외
 buyer19@excon-test.kr</t>
   </si>
@@ -339,7 +353,7 @@
     <t>B09</t>
   </si>
   <si>
-    <t xml:space="preserve">엄품질상사
+    <t>엄품질상사
 엄품질
 buyer20@excon-test.kr</t>
   </si>
@@ -374,23 +388,39 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -415,17 +445,25 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -434,9 +472,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -772,9 +816,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
@@ -783,700 +827,700 @@
     <col min="5" max="10" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5">
+        <v>46169</v>
+      </c>
+      <c r="F1" s="5">
+        <v>46169</v>
+      </c>
+      <c r="G1" s="5">
+        <v>46169</v>
+      </c>
+      <c r="H1" s="5">
+        <v>46169</v>
+      </c>
+      <c r="I1" s="5">
+        <v>46169</v>
+      </c>
+      <c r="J1" s="5">
+        <v>46169</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" ht="90" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" ht="90" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" ht="90" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" ht="90" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" ht="90" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="E8" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" ht="90" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="E9" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="J9" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" ht="90" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="E10" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="J10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="J10" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" ht="90" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="E11" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="I11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="J11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="J11" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" ht="90" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="E12" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="I12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="J12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J12" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" ht="90" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="E13" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" ht="90" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="E14" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" ht="90" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="E15" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" ht="90" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="E16" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="17" ht="90" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="E17" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" ht="90" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="E18" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" ht="90" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="E19" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" ht="90" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="E20" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" ht="90" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="E21" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="22" ht="90" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="E22" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1486,56 +1530,58 @@
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>88</v>
-      </c>
-    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>